--- a/DocDesign/RandomTool/ServerID记录.xlsx
+++ b/DocDesign/RandomTool/ServerID记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\DocDesign\RandomTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A735F0-90BE-4053-B124-002982945A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9643B7-A14E-4034-9B38-A3E484BD72EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32160" yWindow="2940" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36510" yWindow="2475" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>ServerID</t>
   </si>
@@ -79,6 +79,9 @@
     <t>优米</t>
   </si>
   <si>
+    <t>YummySlot</t>
+  </si>
+  <si>
     <t>音乐狂潮</t>
   </si>
   <si>
@@ -289,85 +292,93 @@
     <t>GreedyGenie</t>
   </si>
   <si>
+    <t>职业摩天轮</t>
+  </si>
+  <si>
+    <t>水果圈</t>
+  </si>
+  <si>
+    <t>筛盅</t>
+  </si>
+  <si>
+    <t>Dice</t>
+  </si>
+  <si>
+    <t>豪车汇</t>
+  </si>
+  <si>
+    <t>LuxuryCar</t>
+  </si>
+  <si>
+    <t>德州扑克</t>
+  </si>
+  <si>
+    <t>new77</t>
+  </si>
+  <si>
+    <t>狮子摩天轮</t>
+  </si>
+  <si>
+    <t>GreedyLion</t>
+  </si>
+  <si>
+    <t>海盗捕鱼2.0（JP）</t>
+  </si>
+  <si>
+    <t>疯狂足球</t>
+  </si>
+  <si>
+    <t>kitty摩天轮</t>
+  </si>
+  <si>
+    <t>GreedyKitty</t>
+  </si>
+  <si>
+    <t>美食摩天轮</t>
+  </si>
+  <si>
+    <t>水果摩天轮</t>
+  </si>
+  <si>
+    <t>GreedyFruit</t>
+  </si>
+  <si>
+    <t>GreedyLionR</t>
+  </si>
+  <si>
+    <t>猴子摩天轮</t>
+  </si>
+  <si>
+    <t>GreedyPro</t>
+  </si>
+  <si>
+    <t>小鸡快跑</t>
+  </si>
+  <si>
+    <t>大胃王</t>
+  </si>
+  <si>
+    <t>Bigeater</t>
+  </si>
+  <si>
+    <t>豪车汇R</t>
+  </si>
+  <si>
+    <t>LuxuryCarR</t>
+  </si>
+  <si>
+    <t>皇家金花</t>
+  </si>
+  <si>
+    <t>RoyalTeenPatti</t>
+  </si>
+  <si>
     <t>万人水果机</t>
-  </si>
-  <si>
-    <t>职业摩天轮</t>
-  </si>
-  <si>
-    <t>水果圈</t>
-  </si>
-  <si>
-    <t>筛盅</t>
-  </si>
-  <si>
-    <t>Dice</t>
-  </si>
-  <si>
-    <t>豪车汇</t>
-  </si>
-  <si>
-    <t>LuxuryCar</t>
-  </si>
-  <si>
-    <t>德州扑克</t>
-  </si>
-  <si>
-    <t>new77</t>
-  </si>
-  <si>
-    <t>狮子摩天轮</t>
-  </si>
-  <si>
-    <t>GreedyLion</t>
-  </si>
-  <si>
-    <t>海盗捕鱼2.0（JP）</t>
-  </si>
-  <si>
-    <t>疯狂足球</t>
-  </si>
-  <si>
-    <t>kitty摩天轮</t>
-  </si>
-  <si>
-    <t>GreedyKitty</t>
-  </si>
-  <si>
-    <t>美食摩天轮</t>
-  </si>
-  <si>
-    <t>水果摩天轮</t>
-  </si>
-  <si>
-    <t>GreedyFruit</t>
-  </si>
-  <si>
-    <t>GreedyLionR</t>
-  </si>
-  <si>
-    <t>猴子摩天轮</t>
-  </si>
-  <si>
-    <t>GreedyPro</t>
-  </si>
-  <si>
-    <t>小鸡快跑</t>
-  </si>
-  <si>
-    <t>大胃王</t>
-  </si>
-  <si>
-    <t>Bigeater</t>
-  </si>
-  <si>
-    <t>豪车汇R</t>
-  </si>
-  <si>
-    <t>LuxuryCarR</t>
-  </si>
-  <si>
-    <t>YummySlot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LuckyFruits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>多人</t>
@@ -424,7 +435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -439,6 +450,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -805,6 +819,9 @@
       <c r="B8" t="s">
         <v>12</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -814,7 +831,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -825,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
@@ -836,7 +853,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
@@ -847,10 +864,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
@@ -861,10 +878,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -875,10 +892,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
         <v>8</v>
@@ -889,10 +906,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
@@ -903,10 +920,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -917,10 +934,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -931,10 +948,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
@@ -945,10 +962,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
@@ -959,10 +976,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
@@ -973,10 +990,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
@@ -987,10 +1004,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
@@ -1001,10 +1018,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.15">
@@ -1012,10 +1032,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
@@ -1026,10 +1046,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
@@ -1040,10 +1060,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
@@ -1051,10 +1074,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1065,7 +1088,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
@@ -1073,13 +1096,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>110</v>
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
@@ -1087,10 +1110,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
@@ -1098,10 +1124,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
@@ -1109,10 +1138,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" t="s">
         <v>8</v>
@@ -1123,10 +1152,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
@@ -1137,10 +1166,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
@@ -1148,10 +1180,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
@@ -1159,10 +1194,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
@@ -1170,10 +1208,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
         <v>8</v>
@@ -1184,10 +1222,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -1198,10 +1236,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -1212,10 +1250,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1223,10 +1264,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
@@ -1234,10 +1278,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -1248,10 +1292,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
@@ -1259,10 +1306,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -1270,20 +1320,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" s="3"/>
+      <c r="B46" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
@@ -1313,6 +1371,9 @@
       <c r="C49" s="3" t="s">
         <v>87</v>
       </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
@@ -1324,8 +1385,8 @@
       <c r="C50" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D50" t="s">
-        <v>5</v>
+      <c r="D50" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
@@ -1408,6 +1469,9 @@
       <c r="C58" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="D58" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
@@ -1419,6 +1483,9 @@
       <c r="C59" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
@@ -1471,8 +1538,17 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>109</v>
+      </c>
       <c r="C64" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
